--- a/data/trans_bre/IP07_C13_R_2023-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP07_C13_R_2023-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,191 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,09</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6,52</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-4,28</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-2,7</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>90,86%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-38,63%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-59,72%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.08690603153316268</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>6.515952203432303</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-4.284547309300156</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-2.701258143473886</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.01384927351708968</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.9085544465845122</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.3863489968939048</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.5972290934389352</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-6,25; 7,4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-1,37; 15,77</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-12,53; 3,48</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-11,14; 2,72</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-69,44; 280,13</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-19,01; 412,05</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-82,2; 68,66</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-6.248708358320727</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-1.368850239783916</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-12.53034399501146</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-11.1397729335642</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.6943626188468945</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.1900931025076389</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.8219760256029044</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>7.397345805771008</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>15.76943705481532</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3.477979811942407</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>2.716247877650605</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>2.801331486826169</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>4.120453782111502</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.6865843823062627</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2,72</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-6,42</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-4,14</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,84</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>73,67%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-34,04%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-34,8%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>986,63%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,0; 8,14</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-15,55; 1,5</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-10,47; 2,0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1,56; 13,53</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-46,2; 505,45</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-64,68; 12,17</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-67,96; 27,24</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>2.717218678099412</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-6.42422568482478</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-4.141987039655722</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>5.835507448853254</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.736740405817128</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.3404186756956761</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.3479901895905964</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>9.866265405075712</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,73</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9,22</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,33</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,68</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>59,92%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-3,32%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>479,04%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.998517932403224</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-15.54709276923157</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-10.47198726283398</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>1.562808496050705</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.4620280118581848</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.6467657268059267</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.6795568328084258</v>
+      </c>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-2,93; 8,01</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,44; 20,02</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-9,28; 7,53</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-0,55; 10,87</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,66; 369,64</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-66,66; 145,11</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>8.144031497415346</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.504671826630392</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.996402531229476</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>13.52639051572983</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>5.054547499316136</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.1216797703371551</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.2724470492401219</v>
+      </c>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +811,285 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,13</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7,45</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4,23</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,65</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>85,78%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>57,5%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19,1%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>1.730511117597054</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>9.223397400398792</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.3333834753230819</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>2.677502390696888</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.5991608439022831</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.88712185356468</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.03315343051153168</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>4.790391835071141</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-4,63; 5,46</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-0,24; 16,82</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,58; 10,96</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-6,56; 6,19</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-85,15; 390,17</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-8,38; 356,58</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-30,71; 247,39</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-2.925638500970449</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.43539410403737</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-9.277684230618039</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-0.5548636202626034</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="n">
+        <v>0.006575406939077413</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.6665667965834395</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>8.012869615572759</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>20.01948686343363</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>7.526429945673889</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>10.86721138475987</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="n">
+        <v>3.696435627306193</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.451141452386103</v>
+      </c>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1274621850755955</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>7.45426402466631</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>4.234541578657843</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.653857129706227</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.03423730269835966</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.8577642914107856</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.5749596734502103</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.1910490403311414</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.625690493241559</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-0.2403622870931484</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.576956994830624</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-6.556266716649824</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.8514592265165599</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.08384144367137716</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.3071160015661984</v>
+      </c>
+      <c r="J14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5.457781015071273</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>16.82395785434819</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>10.9638792474746</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>6.194905193062121</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>3.901675719086594</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>3.565758667445649</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>2.473934970830938</v>
+      </c>
+      <c r="J15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,26</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3,52</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,93</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,29</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>30,59%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>30,1%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-9,24%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>122,78%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,23; 4,05</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-0,82; 7,88</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-4,68; 2,94</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-0,12; 5,92</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-25,9; 139,95</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-7,65; 77,65</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-38,98; 36,91</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-21,64; 663,43</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>1.256523321234811</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>3.519862792742411</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.9290477197198401</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>2.291262253806713</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.3059147818965136</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.3010424907979359</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.09244894810078427</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>1.227772544485084</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.232059047718384</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.821895554488716</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-4.680261354169793</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-0.121394541852949</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.2589787479455485</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.07650656857161593</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.389843931856632</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.2163652148189736</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>4.054320322328077</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>7.876324349366472</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.939975814443715</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>5.919708239842252</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1.399483390345514</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.7765316556841709</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.3690811556803936</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>6.634316962236261</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1097,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
